--- a/erp-server/erp-server-oms/src/main/resources/excel/b2cUpdateTemplate.xlsx
+++ b/erp-server/erp-server-oms/src/main/resources/excel/b2cUpdateTemplate.xlsx
@@ -29,9 +29,16 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
-  <si>
-    <r>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -46,6 +53,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -60,6 +74,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -74,6 +95,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -88,6 +116,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -102,6 +137,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -116,6 +158,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -135,6 +184,20 @@
     <t>订单分类</t>
   </si>
   <si>
+    <r>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>订单类型</t>
+    </r>
+  </si>
+  <si>
     <t>订单备注</t>
   </si>
   <si>
@@ -154,6 +217,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -174,6 +244,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -191,6 +268,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -208,6 +292,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -240,6 +331,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -254,6 +352,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -271,6 +376,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -925,7 +1037,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -940,6 +1052,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1252,13 +1367,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AG7"/>
+  <dimension ref="A1:AH7"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="6"/>
   <cols>
     <col min="7" max="7" width="21.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:33">
+    <row r="1" s="1" customFormat="1" spans="1:34">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1286,7 +1401,7 @@
       <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" s="5" t="s">
         <v>9</v>
       </c>
       <c r="K1" s="3" t="s">
@@ -1304,31 +1419,31 @@
       <c r="O1" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="P1" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="3" t="s">
+      <c r="Q1" s="2" t="s">
         <v>16</v>
       </c>
       <c r="R1" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="2" t="s">
+      <c r="S1" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="3" t="s">
+      <c r="T1" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="2" t="s">
+      <c r="U1" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="3" t="s">
+      <c r="V1" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="2" t="s">
+      <c r="W1" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="3" t="s">
+      <c r="X1" s="2" t="s">
         <v>23</v>
       </c>
       <c r="Y1" s="3" t="s">
@@ -1346,17 +1461,20 @@
       <c r="AC1" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="AD1" s="2" t="s">
+      <c r="AD1" s="3" t="s">
         <v>29</v>
       </c>
       <c r="AE1" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="AF1" s="3" t="s">
+      <c r="AF1" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="AG1" s="2" t="s">
+      <c r="AG1" s="3" t="s">
         <v>32</v>
+      </c>
+      <c r="AH1" s="2" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="7" spans="6:6">

--- a/erp-server/erp-server-oms/src/main/resources/excel/b2cUpdateTemplate.xlsx
+++ b/erp-server/erp-server-oms/src/main/resources/excel/b2cUpdateTemplate.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="69">
   <si>
     <r>
       <rPr>
@@ -185,6 +185,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -394,6 +401,111 @@
       </rPr>
       <t>真实售价</t>
     </r>
+  </si>
+  <si>
+    <t>CZK</t>
+  </si>
+  <si>
+    <t>PLN</t>
+  </si>
+  <si>
+    <t>GBP</t>
+  </si>
+  <si>
+    <t>EUR</t>
+  </si>
+  <si>
+    <t>THB</t>
+  </si>
+  <si>
+    <t>BRL</t>
+  </si>
+  <si>
+    <t>MXN</t>
+  </si>
+  <si>
+    <t>INR</t>
+  </si>
+  <si>
+    <t>KES</t>
+  </si>
+  <si>
+    <t>KRW</t>
+  </si>
+  <si>
+    <t>MOP</t>
+  </si>
+  <si>
+    <t>HKD</t>
+  </si>
+  <si>
+    <t>IDR</t>
+  </si>
+  <si>
+    <t>PHP</t>
+  </si>
+  <si>
+    <t>JPY</t>
+  </si>
+  <si>
+    <t>CAD</t>
+  </si>
+  <si>
+    <t>SGD</t>
+  </si>
+  <si>
+    <t>CNY</t>
+  </si>
+  <si>
+    <t>USD</t>
+  </si>
+  <si>
+    <t>AUD</t>
+  </si>
+  <si>
+    <t>SEK</t>
+  </si>
+  <si>
+    <t>MYR</t>
+  </si>
+  <si>
+    <t>TWD</t>
+  </si>
+  <si>
+    <t>AED</t>
+  </si>
+  <si>
+    <t>DKK</t>
+  </si>
+  <si>
+    <t>RUB</t>
+  </si>
+  <si>
+    <t>ZAR</t>
+  </si>
+  <si>
+    <t>NOK</t>
+  </si>
+  <si>
+    <t>CHF</t>
+  </si>
+  <si>
+    <t>SAR</t>
+  </si>
+  <si>
+    <t>TRY</t>
+  </si>
+  <si>
+    <t>NZD</t>
+  </si>
+  <si>
+    <t>HUF</t>
+  </si>
+  <si>
+    <t>ILS</t>
+  </si>
+  <si>
+    <t>VND</t>
   </si>
 </sst>
 </file>
@@ -1477,10 +1589,20 @@
         <v>33</v>
       </c>
     </row>
+    <row r="2" spans="6:6">
+      <c r="F2" t="s">
+        <v>34</v>
+      </c>
+    </row>
     <row r="7" spans="6:6">
       <c r="F7" s="4"/>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F$1:F$1048576">
+      <formula1>"CZK,PLN,GBP,EUR,THB,BRL,MXN,INR,KES,KRW,MOP,HKD,IDR,PHP,JPY,CAD,SGD,CNY,USD,AUD,SEK,MYR,TWD,AED,DKK,RUB,ZAR,NOK,CHF,SAR,TRY,NZD,HUF,ILS,VND"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
@@ -1490,9 +1612,185 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1"/>
+  <dimension ref="A1:A35"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1">
+      <c r="A2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1">
+      <c r="A4" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1">
+      <c r="A13" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1">
+      <c r="A14" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1">
+      <c r="A15" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1">
+      <c r="A16" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1">
+      <c r="A20" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1">
+      <c r="A22" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1">
+      <c r="A24" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1">
+      <c r="A25" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1">
+      <c r="A26" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1">
+      <c r="A27" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1">
+      <c r="A28" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1">
+      <c r="A29" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1">
+      <c r="A30" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1">
+      <c r="A31" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1">
+      <c r="A32" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1">
+      <c r="A34" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1">
+      <c r="A35" t="s">
+        <v>68</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>

--- a/erp-server/erp-server-oms/src/main/resources/excel/b2cUpdateTemplate.xlsx
+++ b/erp-server/erp-server-oms/src/main/resources/excel/b2cUpdateTemplate.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="70">
   <si>
     <r>
       <rPr>
@@ -326,6 +326,9 @@
   </si>
   <si>
     <t>收件人税号</t>
+  </si>
+  <si>
+    <t>IE号</t>
   </si>
   <si>
     <t>收件人地址1</t>
@@ -1479,13 +1482,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AH7"/>
+  <dimension ref="A1:AI7"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="6"/>
   <cols>
     <col min="7" max="7" width="21.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:34">
+    <row r="1" s="1" customFormat="1" spans="1:35">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1576,22 +1579,25 @@
       <c r="AD1" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="AE1" s="2" t="s">
+      <c r="AE1" s="3" t="s">
         <v>30</v>
       </c>
       <c r="AF1" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="AG1" s="3" t="s">
+      <c r="AG1" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="AH1" s="2" t="s">
+      <c r="AH1" s="3" t="s">
         <v>33</v>
+      </c>
+      <c r="AI1" s="2" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="2" spans="6:6">
       <c r="F2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="7" spans="6:6">
@@ -1617,177 +1623,177 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="32" spans="1:1">
       <c r="A32" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-oms/src/main/resources/excel/b2cUpdateTemplate.xlsx
+++ b/erp-server/erp-server-oms/src/main/resources/excel/b2cUpdateTemplate.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -211,7 +211,7 @@
     <t>物流渠道</t>
   </si>
   <si>
-    <t>跟踪号</t>
+    <t>运单号</t>
   </si>
   <si>
     <t>包装尺寸(长*宽*高)</t>
